--- a/card_list.xlsx
+++ b/card_list.xlsx
@@ -1,16 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24334"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\liuyuxuan\Documents\arknights-mizuki\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07CA4375-39AE-4058-B926-162B789C8B33}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowWidth="25590" windowHeight="11200"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="14620" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="卡牌列表" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">卡牌列表!$A$1:$I$48</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">卡牌列表!$A$1:$I$53</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -21,16 +27,17 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="357" uniqueCount="183">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="396" uniqueCount="206">
   <si>
     <t>#</t>
   </si>
@@ -147,9 +154,6 @@
     <t>损伤</t>
   </si>
   <si>
-    <t>伤害3</t>
-  </si>
-  <si>
     <t>受到2点伤害。</t>
   </si>
   <si>
@@ -177,10 +181,6 @@
     <t>损伤3</t>
   </si>
   <si>
-    <t>随机给予敌人3层损伤
-重复{Times:diff()}次</t>
-  </si>
-  <si>
     <t>触手打击</t>
   </si>
   <si>
@@ -250,9 +250,6 @@
     <t>伤害4，抽牌3</t>
   </si>
   <si>
-    <t>伤害-2，伤害-2</t>
-  </si>
-  <si>
     <t>失去4点生命，抽3张牌。</t>
   </si>
   <si>
@@ -262,9 +259,6 @@
     <t>ShadowFlagPower1</t>
   </si>
   <si>
-    <t>获得Innate</t>
-  </si>
-  <si>
     <t>回合内每打出一张急速牌，回合结束时对敌人造成1点伤害。</t>
   </si>
   <si>
@@ -272,9 +266,6 @@
   </si>
   <si>
     <t>伤害3，攻击附带损伤1，力量(下一击)3</t>
-  </si>
-  <si>
-    <t>攻击附带损伤+1，伤害-1，伤害-1</t>
   </si>
   <si>
     <t>失去3点生命，你的下一次攻击附带1层损伤
@@ -564,15 +555,6 @@
     <t>爆条所需层数-2</t>
   </si>
   <si>
-    <t>海水冷漠</t>
-  </si>
-  <si>
-    <t>防御6</t>
-  </si>
-  <si>
-    <t>获得6/9点格挡，从抽牌堆中选择一张牌加入手牌</t>
-  </si>
-  <si>
     <t>肢体分裂</t>
   </si>
   <si>
@@ -586,19 +568,107 @@
   </si>
   <si>
     <t>对所有敌人施加2层侵蚀，抽一张牌，如果肢体分裂在你的弃牌堆中，回复8点生命，</t>
+  </si>
+  <si>
+    <t>TODO</t>
+  </si>
+  <si>
+    <t>(+2,+3)</t>
+  </si>
+  <si>
+    <t>(+1)</t>
+  </si>
+  <si>
+    <t>(+2,+1)</t>
+  </si>
+  <si>
+    <t>伤害2</t>
+  </si>
+  <si>
+    <t>普通(衍生）</t>
+  </si>
+  <si>
+    <t>(+4,+1)</t>
+  </si>
+  <si>
+    <t>（+1）次</t>
+  </si>
+  <si>
+    <t>随机给予敌人3层损伤
+重复3次</t>
+  </si>
+  <si>
+    <t>（+0，+1）</t>
+  </si>
+  <si>
+    <t>忘了</t>
+  </si>
+  <si>
+    <t>（+1）</t>
+  </si>
+  <si>
+    <t>（+2伤害）</t>
+  </si>
+  <si>
+    <t>伤害5</t>
+  </si>
+  <si>
+    <t>回响1</t>
+  </si>
+  <si>
+    <t>伤害-2</t>
+  </si>
+  <si>
+    <t>获得固有</t>
+  </si>
+  <si>
+    <t>wangle</t>
+  </si>
+  <si>
+    <t>（+1层）</t>
+  </si>
+  <si>
+    <t>收获</t>
+  </si>
+  <si>
+    <t>普通（衍生）</t>
+  </si>
+  <si>
+    <t>打4收获3</t>
+  </si>
+  <si>
+    <t>造成4点伤害，收获3</t>
+  </si>
+  <si>
+    <t>收获：召唤钵海收割者，重复召唤则给予其等量的海嗣化，每层提高一点伤害</t>
+  </si>
+  <si>
+    <t>收割者：每回合一次，a4</t>
+  </si>
+  <si>
+    <t>漂浮</t>
+  </si>
+  <si>
+    <t>抽2，漂浮3</t>
+  </si>
+  <si>
+    <t>抽3</t>
+  </si>
+  <si>
+    <t>漂浮3，抽2张牌</t>
+  </si>
+  <si>
+    <t>漂浮：召唤浮海漂移者，重复召唤同上</t>
+  </si>
+  <si>
+    <t>漂浮者：每回合1次，5甲</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="42" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
-    <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-  </numFmts>
-  <fonts count="23">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -625,152 +695,8 @@
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="39">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -813,194 +739,8 @@
         <bgColor rgb="FFE4DFEC"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="10">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -1025,251 +765,44 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FFB2B2B2"/>
+        <color auto="1"/>
       </left>
       <right style="thin">
-        <color rgb="FFB2B2B2"/>
+        <color auto="1"/>
       </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
       <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
+        <color indexed="64"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left/>
-      <right/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
       <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
       <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
+        <color indexed="64"/>
       </bottom>
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="49">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="176" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="9" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="10" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="10" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="11" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1301,62 +834,27 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="49">
+  <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -1641,13 +1139,13 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:I88"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:K88"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
@@ -1658,9 +1156,11 @@
     <col min="7" max="7" width="24" customWidth="1"/>
     <col min="8" max="8" width="22" customWidth="1"/>
     <col min="9" max="9" width="65" customWidth="1"/>
+    <col min="10" max="10" width="41.08984375" customWidth="1"/>
+    <col min="11" max="11" width="22.1796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="24" customHeight="1" spans="1:9">
+    <row r="1" spans="1:9" ht="24" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1689,7 +1189,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" ht="36" customHeight="1" spans="1:9">
+    <row r="2" spans="1:9" ht="36" customHeight="1">
       <c r="A2" s="2">
         <v>1</v>
       </c>
@@ -1718,7 +1218,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="3" ht="36" customHeight="1" spans="1:9">
+    <row r="3" spans="1:9" ht="36" customHeight="1">
       <c r="A3" s="2">
         <v>2</v>
       </c>
@@ -1747,7 +1247,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="4" ht="36" customHeight="1" spans="1:9">
+    <row r="4" spans="1:9" ht="36" customHeight="1">
       <c r="A4" s="2">
         <v>3</v>
       </c>
@@ -1776,7 +1276,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="5" ht="36" customHeight="1" spans="1:9">
+    <row r="5" spans="1:9" ht="36" customHeight="1">
       <c r="A5" s="3">
         <v>4</v>
       </c>
@@ -1799,13 +1299,13 @@
         <v>24</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>12</v>
+        <v>178</v>
       </c>
       <c r="I5" s="3" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="6" ht="36" customHeight="1" spans="1:9">
+    <row r="6" spans="1:9" ht="36" customHeight="1">
       <c r="A6" s="3">
         <v>5</v>
       </c>
@@ -1828,13 +1328,13 @@
         <v>26</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>12</v>
+        <v>176</v>
       </c>
       <c r="I6" s="3" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="7" ht="36" customHeight="1" spans="1:9">
+    <row r="7" spans="1:9" ht="36" customHeight="1">
       <c r="A7" s="3">
         <v>6</v>
       </c>
@@ -1857,13 +1357,13 @@
         <v>30</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>12</v>
+        <v>177</v>
       </c>
       <c r="I7" s="3" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="8" ht="36" customHeight="1" spans="1:9">
+    <row r="8" spans="1:9" ht="36" customHeight="1">
       <c r="A8" s="3">
         <v>7</v>
       </c>
@@ -1892,7 +1392,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="9" ht="36" customHeight="1" spans="1:9">
+    <row r="9" spans="1:9" ht="36" customHeight="1">
       <c r="A9" s="3">
         <v>8</v>
       </c>
@@ -1903,7 +1403,7 @@
         <v>10</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>23</v>
+        <v>180</v>
       </c>
       <c r="E9" s="3">
         <v>1</v>
@@ -1912,21 +1412,21 @@
         <v>33</v>
       </c>
       <c r="G9" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="H9" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I9" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="H9" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="I9" s="3" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="10" ht="36" customHeight="1" spans="1:9">
+    </row>
+    <row r="10" spans="1:9" ht="36" customHeight="1">
       <c r="A10" s="3">
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C10" s="3" t="s">
         <v>10</v>
@@ -1941,21 +1441,21 @@
         <v>12</v>
       </c>
       <c r="G10" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="H10" s="3">
+        <v>4</v>
+      </c>
+      <c r="I10" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="H10" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="I10" s="3" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="11" ht="36" customHeight="1" spans="1:9">
+    </row>
+    <row r="11" spans="1:9" ht="36" customHeight="1">
       <c r="A11" s="3">
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C11" s="3" t="s">
         <v>19</v>
@@ -1970,21 +1470,21 @@
         <v>12</v>
       </c>
       <c r="G11" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="H11" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="I11" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="H11" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="I11" s="3" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="12" ht="36" customHeight="1" spans="1:9">
+    </row>
+    <row r="12" spans="1:9" ht="36" customHeight="1">
       <c r="A12" s="3">
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C12" s="3" t="s">
         <v>19</v>
@@ -1999,21 +1499,21 @@
         <v>12</v>
       </c>
       <c r="G12" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="H12" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="I12" s="3" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" ht="36" customHeight="1">
+      <c r="A13" s="3">
+        <v>12</v>
+      </c>
+      <c r="B13" s="3" t="s">
         <v>47</v>
-      </c>
-      <c r="H12" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="I12" s="3" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="13" ht="36" customHeight="1" spans="1:9">
-      <c r="A13" s="3">
-        <v>12</v>
-      </c>
-      <c r="B13" s="3" t="s">
-        <v>49</v>
       </c>
       <c r="C13" s="3" t="s">
         <v>10</v>
@@ -2028,21 +1528,21 @@
         <v>12</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>12</v>
+        <v>184</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="14" ht="36" customHeight="1" spans="1:9">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" ht="36" customHeight="1">
       <c r="A14" s="3">
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C14" s="3" t="s">
         <v>10</v>
@@ -2057,27 +1557,27 @@
         <v>33</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>12</v>
+        <v>185</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="15" ht="36" customHeight="1" spans="1:9">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" ht="36" customHeight="1">
       <c r="A15" s="4">
         <v>14</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C15" s="4" t="s">
         <v>19</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E15" s="4">
         <v>1</v>
@@ -2086,56 +1586,56 @@
         <v>33</v>
       </c>
       <c r="G15" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="H15" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="I15" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="H15" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="I15" s="4" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="16" ht="36" customHeight="1" spans="1:9">
+    </row>
+    <row r="16" spans="1:9" ht="36" customHeight="1">
       <c r="A16" s="4">
         <v>15</v>
       </c>
       <c r="B16" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="D16" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="E16" s="4">
+        <v>1</v>
+      </c>
+      <c r="F16" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="G16" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="C16" s="4" t="s">
+      <c r="H16" s="4" t="s">
+        <v>186</v>
+      </c>
+      <c r="I16" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="D16" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="E16" s="4">
-        <v>1</v>
-      </c>
-      <c r="F16" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="G16" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="H16" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="I16" s="4" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="17" ht="36" customHeight="1" spans="1:9">
+    </row>
+    <row r="17" spans="1:9" ht="36" customHeight="1">
       <c r="A17" s="4">
         <v>16</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C17" s="4" t="s">
         <v>19</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E17" s="4">
         <v>2</v>
@@ -2144,56 +1644,56 @@
         <v>12</v>
       </c>
       <c r="G17" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="H17" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="I17" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="H17" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="I17" s="4" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="18" ht="36" customHeight="1" spans="1:9">
+    </row>
+    <row r="18" spans="1:9" ht="36" customHeight="1">
       <c r="A18" s="4">
         <v>17</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C18" s="4" t="s">
         <v>10</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E18" s="4">
         <v>1</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>12</v>
+        <v>189</v>
       </c>
       <c r="G18" s="4" t="s">
-        <v>16</v>
+        <v>188</v>
       </c>
       <c r="H18" s="4" t="s">
-        <v>12</v>
+        <v>187</v>
       </c>
       <c r="I18" s="4" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="19" ht="36" customHeight="1" spans="1:9">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" ht="36" customHeight="1">
       <c r="A19" s="4">
         <v>18</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C19" s="4" t="s">
         <v>19</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E19" s="4">
         <v>1</v>
@@ -2202,27 +1702,27 @@
         <v>12</v>
       </c>
       <c r="G19" s="4" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="H19" s="4" t="s">
-        <v>72</v>
+        <v>190</v>
       </c>
       <c r="I19" s="4" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="20" ht="36" customHeight="1" spans="1:9">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" ht="36" customHeight="1">
       <c r="A20" s="4">
         <v>19</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E20" s="4">
         <v>1</v>
@@ -2231,27 +1731,27 @@
         <v>12</v>
       </c>
       <c r="G20" s="4" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="H20" s="4" t="s">
-        <v>76</v>
+        <v>191</v>
       </c>
       <c r="I20" s="4" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="21" ht="36" customHeight="1" spans="1:9">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" ht="36" customHeight="1">
       <c r="A21" s="4">
         <v>20</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="C21" s="4" t="s">
         <v>19</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E21" s="4">
         <v>1</v>
@@ -2260,27 +1760,27 @@
         <v>12</v>
       </c>
       <c r="G21" s="4" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="H21" s="4" t="s">
-        <v>80</v>
+        <v>192</v>
       </c>
       <c r="I21" s="4" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="22" ht="36" customHeight="1" spans="1:9">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" ht="36" customHeight="1">
       <c r="A22" s="4">
         <v>21</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="C22" s="4" t="s">
         <v>10</v>
       </c>
       <c r="D22" s="4" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E22" s="4">
         <v>2</v>
@@ -2289,27 +1789,27 @@
         <v>12</v>
       </c>
       <c r="G22" s="4" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="H22" s="4" t="s">
-        <v>12</v>
+        <v>192</v>
       </c>
       <c r="I22" s="4" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="23" ht="36" customHeight="1" spans="1:9">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" ht="36" customHeight="1">
       <c r="A23" s="4">
         <v>22</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E23" s="4">
         <v>1</v>
@@ -2318,27 +1818,27 @@
         <v>12</v>
       </c>
       <c r="G23" s="4" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="H23" s="4" t="s">
-        <v>12</v>
+        <v>193</v>
       </c>
       <c r="I23" s="4" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="24" ht="36" customHeight="1" spans="1:9">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" ht="36" customHeight="1">
       <c r="A24" s="4">
         <v>23</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="C24" s="4" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="4" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E24" s="4">
         <v>1</v>
@@ -2347,27 +1847,27 @@
         <v>12</v>
       </c>
       <c r="G24" s="4" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="H24" s="4" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="I24" s="4" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="25" ht="36" customHeight="1" spans="1:9">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" ht="36" customHeight="1">
       <c r="A25" s="4">
         <v>24</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="C25" s="4" t="s">
         <v>19</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E25" s="4">
         <v>1</v>
@@ -2379,24 +1879,24 @@
         <v>12</v>
       </c>
       <c r="H25" s="4" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="I25" s="4" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="26" ht="36" customHeight="1" spans="1:9">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" ht="36" customHeight="1">
       <c r="A26" s="4">
         <v>25</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="C26" s="4" t="s">
         <v>19</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E26" s="4">
         <v>2</v>
@@ -2405,56 +1905,56 @@
         <v>33</v>
       </c>
       <c r="G26" s="4" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="H26" s="4" t="s">
         <v>12</v>
       </c>
       <c r="I26" s="4" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="27" ht="36" customHeight="1" spans="1:9">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" ht="36" customHeight="1">
       <c r="A27" s="4">
         <v>26</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="C27" s="4" t="s">
         <v>19</v>
       </c>
       <c r="D27" s="4" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E27" s="4">
         <v>1</v>
       </c>
       <c r="F27" s="4" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="G27" s="4" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="H27" s="4" t="s">
         <v>12</v>
       </c>
       <c r="I27" s="4" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="28" ht="36" customHeight="1" spans="1:9">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" ht="36" customHeight="1">
       <c r="A28" s="4">
         <v>27</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="C28" s="4" t="s">
         <v>10</v>
       </c>
       <c r="D28" s="4" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E28" s="4">
         <v>1</v>
@@ -2463,27 +1963,27 @@
         <v>12</v>
       </c>
       <c r="G28" s="4" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="H28" s="4" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="I28" s="4" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="29" ht="36" customHeight="1" spans="1:9">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" ht="36" customHeight="1">
       <c r="A29" s="4">
         <v>28</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="D29" s="4" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E29" s="4">
         <v>2</v>
@@ -2492,56 +1992,56 @@
         <v>12</v>
       </c>
       <c r="G29" s="4" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="H29" s="4" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="I29" s="4" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="30" ht="36" customHeight="1" spans="1:9">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" ht="36" customHeight="1">
       <c r="A30" s="4">
         <v>29</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="C30" s="4" t="s">
         <v>19</v>
       </c>
       <c r="D30" s="4" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E30" s="4">
         <v>0</v>
       </c>
       <c r="F30" s="4" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="G30" s="4" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="H30" s="4" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="I30" s="4" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="31" ht="36" customHeight="1" spans="1:9">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" ht="36" customHeight="1">
       <c r="A31" s="4">
         <v>30</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="C31" s="4" t="s">
         <v>10</v>
       </c>
       <c r="D31" s="4" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E31" s="4">
         <v>1</v>
@@ -2550,27 +2050,27 @@
         <v>12</v>
       </c>
       <c r="G31" s="4" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="H31" s="4" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="I31" s="4" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="32" ht="36" customHeight="1" spans="1:9">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" ht="36" customHeight="1">
       <c r="A32" s="4">
         <v>31</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="C32" s="4" t="s">
         <v>10</v>
       </c>
       <c r="D32" s="4" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E32" s="4">
         <v>1</v>
@@ -2579,27 +2079,27 @@
         <v>12</v>
       </c>
       <c r="G32" s="4" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="H32" s="4" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="I32" s="4" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="33" ht="36" customHeight="1" spans="1:9">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" ht="36" customHeight="1">
       <c r="A33" s="4">
         <v>32</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="C33" s="4" t="s">
         <v>19</v>
       </c>
       <c r="D33" s="4" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E33" s="4">
         <v>1</v>
@@ -2608,27 +2108,27 @@
         <v>12</v>
       </c>
       <c r="G33" s="4" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="H33" s="4" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="I33" s="4" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="34" ht="36" customHeight="1" spans="1:9">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9" ht="36" customHeight="1">
       <c r="A34" s="4">
         <v>33</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="C34" s="4" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="D34" s="4" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E34" s="4">
         <v>1</v>
@@ -2637,56 +2137,56 @@
         <v>12</v>
       </c>
       <c r="G34" s="4" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="H34" s="4" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="I34" s="4" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="35" ht="36" customHeight="1" spans="1:9">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9" ht="36" customHeight="1">
       <c r="A35" s="4">
         <v>34</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="C35" s="4" t="s">
         <v>19</v>
       </c>
       <c r="D35" s="4" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E35" s="4">
         <v>0</v>
       </c>
       <c r="F35" s="4" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="G35" s="4" t="s">
         <v>12</v>
       </c>
       <c r="H35" s="4" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="I35" s="4" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="36" ht="36" customHeight="1" spans="1:9">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9" ht="36" customHeight="1">
       <c r="A36" s="4">
         <v>35</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="C36" s="4" t="s">
         <v>10</v>
       </c>
       <c r="D36" s="4" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E36" s="4">
         <v>2</v>
@@ -2695,56 +2195,56 @@
         <v>12</v>
       </c>
       <c r="G36" s="4" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="H36" s="4" t="s">
         <v>12</v>
       </c>
       <c r="I36" s="4" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="37" ht="36" customHeight="1" spans="1:9">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9" ht="36" customHeight="1">
       <c r="A37" s="4">
         <v>36</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="C37" s="4" t="s">
         <v>19</v>
       </c>
       <c r="D37" s="4" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E37" s="4">
         <v>1</v>
       </c>
       <c r="F37" s="4" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="G37" s="4" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="H37" s="4" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="I37" s="4" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="38" ht="36" customHeight="1" spans="1:9">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9" ht="36" customHeight="1">
       <c r="A38" s="4">
         <v>37</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="C38" s="4" t="s">
         <v>10</v>
       </c>
       <c r="D38" s="4" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E38" s="4">
         <v>1</v>
@@ -2753,27 +2253,27 @@
         <v>12</v>
       </c>
       <c r="G38" s="4" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="H38" s="4" t="s">
         <v>12</v>
       </c>
       <c r="I38" s="4" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="39" ht="36" customHeight="1" spans="1:9">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9" ht="36" customHeight="1">
       <c r="A39" s="4">
         <v>38</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="C39" s="4" t="s">
         <v>19</v>
       </c>
       <c r="D39" s="4" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E39" s="4">
         <v>1</v>
@@ -2782,27 +2282,27 @@
         <v>29</v>
       </c>
       <c r="G39" s="4" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="H39" s="4" t="s">
         <v>12</v>
       </c>
       <c r="I39" s="4" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="40" ht="36" customHeight="1" spans="1:9">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9" ht="36" customHeight="1">
       <c r="A40" s="5">
         <v>39</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="C40" s="5" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="D40" s="5" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="E40" s="5">
         <v>3</v>
@@ -2811,27 +2311,27 @@
         <v>12</v>
       </c>
       <c r="G40" s="5" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="H40" s="5" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="I40" s="5" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="41" ht="36" customHeight="1" spans="1:9">
+    <row r="41" spans="1:9" ht="36" customHeight="1">
       <c r="A41" s="5">
         <v>40</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="C41" s="5" t="s">
         <v>19</v>
       </c>
       <c r="D41" s="5" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="E41" s="5">
         <v>1</v>
@@ -2840,27 +2340,27 @@
         <v>12</v>
       </c>
       <c r="G41" s="5" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="H41" s="5" t="s">
         <v>12</v>
       </c>
       <c r="I41" s="5" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="42" ht="36" customHeight="1" spans="1:9">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9" ht="36" customHeight="1">
       <c r="A42" s="5">
         <v>41</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="C42" s="5" t="s">
         <v>19</v>
       </c>
       <c r="D42" s="5" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="E42" s="5">
         <v>2</v>
@@ -2872,24 +2372,24 @@
         <v>12</v>
       </c>
       <c r="H42" s="5" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="I42" s="5" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="43" ht="36" customHeight="1" spans="1:9">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9" ht="36" customHeight="1">
       <c r="A43" s="5">
         <v>42</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="C43" s="5" t="s">
         <v>19</v>
       </c>
       <c r="D43" s="5" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="E43" s="5">
         <v>1</v>
@@ -2898,27 +2398,27 @@
         <v>12</v>
       </c>
       <c r="G43" s="5" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="H43" s="5" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="I43" s="5" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="44" ht="36" customHeight="1" spans="1:9">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9" ht="36" customHeight="1">
       <c r="A44" s="5">
         <v>43</v>
       </c>
       <c r="B44" s="5" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="C44" s="5" t="s">
         <v>19</v>
       </c>
       <c r="D44" s="5" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="E44" s="5">
         <v>2</v>
@@ -2927,27 +2427,27 @@
         <v>12</v>
       </c>
       <c r="G44" s="5" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="H44" s="5" t="s">
-        <v>160</v>
+        <v>155</v>
       </c>
       <c r="I44" s="5" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="45" ht="36" customHeight="1" spans="1:9">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="45" spans="1:9" ht="36" customHeight="1">
       <c r="A45" s="5">
         <v>44</v>
       </c>
       <c r="B45" s="5" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="C45" s="5" t="s">
         <v>19</v>
       </c>
       <c r="D45" s="5" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="E45" s="5">
         <v>1</v>
@@ -2959,24 +2459,24 @@
         <v>30</v>
       </c>
       <c r="H45" s="5" t="s">
-        <v>160</v>
+        <v>155</v>
       </c>
       <c r="I45" s="5" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="46" ht="36" customHeight="1" spans="1:9">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="46" spans="1:9" ht="36" customHeight="1">
       <c r="A46" s="5">
         <v>45</v>
       </c>
       <c r="B46" s="5" t="s">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="C46" s="5" t="s">
         <v>10</v>
       </c>
       <c r="D46" s="5" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="E46" s="5">
         <v>1</v>
@@ -2991,21 +2491,21 @@
         <v>12</v>
       </c>
       <c r="I46" s="5" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="47" ht="36" customHeight="1" spans="1:9">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="47" spans="1:9" ht="36" customHeight="1">
       <c r="A47" s="5">
         <v>46</v>
       </c>
       <c r="B47" s="5" t="s">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="C47" s="5" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="D47" s="5" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="E47" s="5">
         <v>2</v>
@@ -3014,27 +2514,27 @@
         <v>12</v>
       </c>
       <c r="G47" s="5" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="H47" s="5" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="I47" s="5" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="48" ht="36" customHeight="1" spans="1:9">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="48" spans="1:9" ht="36" customHeight="1">
       <c r="A48" s="6">
         <v>47</v>
       </c>
       <c r="B48" s="6" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="C48" s="6" t="s">
         <v>10</v>
       </c>
       <c r="D48" s="6" t="s">
-        <v>170</v>
+        <v>165</v>
       </c>
       <c r="E48" s="6">
         <v>1</v>
@@ -3043,27 +2543,27 @@
         <v>12</v>
       </c>
       <c r="G48" s="6" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="H48" s="6" t="s">
         <v>12</v>
       </c>
       <c r="I48" s="6" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="49" ht="30" customHeight="1" spans="1:9">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="49" spans="1:11" ht="30" customHeight="1">
       <c r="A49" s="7">
         <v>48</v>
       </c>
       <c r="B49" s="7" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="C49" s="7" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="D49" s="7" t="s">
-        <v>170</v>
+        <v>165</v>
       </c>
       <c r="E49" s="7">
         <v>1</v>
@@ -3072,18 +2572,18 @@
       <c r="G49" s="9"/>
       <c r="H49" s="8"/>
       <c r="I49" s="7" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="50" ht="30" customHeight="1" spans="1:9">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="50" spans="1:11" ht="30" customHeight="1">
       <c r="A50" s="3">
         <v>49</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>175</v>
+        <v>194</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="D50" s="3" t="s">
         <v>23</v>
@@ -3091,21 +2591,29 @@
       <c r="E50" s="3">
         <v>1</v>
       </c>
-      <c r="F50" s="3"/>
+      <c r="F50" s="3" t="s">
+        <v>194</v>
+      </c>
       <c r="G50" s="3" t="s">
-        <v>176</v>
+        <v>196</v>
       </c>
       <c r="H50" s="3"/>
       <c r="I50" s="3" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="51" ht="30" customHeight="1" spans="1:9">
+        <v>197</v>
+      </c>
+      <c r="J50" s="11" t="s">
+        <v>198</v>
+      </c>
+      <c r="K50" s="11" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="51" spans="1:11" ht="30" customHeight="1">
       <c r="A51" s="3">
         <v>50</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>178</v>
+        <v>170</v>
       </c>
       <c r="C51" s="3" t="s">
         <v>19</v>
@@ -3118,54 +2626,92 @@
       </c>
       <c r="F51" s="3"/>
       <c r="G51" s="3" t="s">
-        <v>179</v>
+        <v>171</v>
       </c>
       <c r="H51" s="3"/>
       <c r="I51" s="3" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="52" ht="30" customHeight="1" spans="1:9">
+        <v>172</v>
+      </c>
+      <c r="J51" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="52" spans="1:11" ht="30" customHeight="1">
       <c r="A52" s="3">
         <v>51</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>181</v>
+        <v>173</v>
       </c>
       <c r="C52" s="3" t="s">
         <v>19</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>23</v>
+        <v>195</v>
       </c>
       <c r="E52" s="3">
         <v>1</v>
       </c>
       <c r="F52" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="G52" s="3"/>
+        <v>106</v>
+      </c>
+      <c r="G52" s="3" t="s">
+        <v>63</v>
+      </c>
       <c r="H52" s="3"/>
       <c r="I52" s="3" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="53" ht="30" customHeight="1" spans="1:1">
+        <v>174</v>
+      </c>
+      <c r="J52" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="53" spans="1:11" ht="30" customHeight="1">
       <c r="A53" s="10">
         <v>52</v>
       </c>
-    </row>
-    <row r="54" ht="30" customHeight="1"/>
-    <row r="55" ht="30" customHeight="1"/>
-    <row r="56" ht="30" customHeight="1"/>
-    <row r="57" ht="30" customHeight="1"/>
-    <row r="58" ht="30" customHeight="1"/>
-    <row r="59" ht="30" customHeight="1"/>
-    <row r="60" ht="30" customHeight="1"/>
-    <row r="61" ht="30" customHeight="1"/>
-    <row r="62" ht="30" customHeight="1"/>
-    <row r="63" ht="30" customHeight="1"/>
-    <row r="64" ht="30" customHeight="1"/>
+      <c r="B53" s="12" t="s">
+        <v>200</v>
+      </c>
+      <c r="C53" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="D53" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="E53" s="12">
+        <v>2</v>
+      </c>
+      <c r="F53" s="13" t="s">
+        <v>200</v>
+      </c>
+      <c r="G53" s="12" t="s">
+        <v>201</v>
+      </c>
+      <c r="H53" s="12" t="s">
+        <v>202</v>
+      </c>
+      <c r="I53" s="12" t="s">
+        <v>203</v>
+      </c>
+      <c r="J53" s="12" t="s">
+        <v>204</v>
+      </c>
+      <c r="K53" s="12" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="54" spans="1:11" ht="30" customHeight="1"/>
+    <row r="55" spans="1:11" ht="30" customHeight="1"/>
+    <row r="56" spans="1:11" ht="30" customHeight="1"/>
+    <row r="57" spans="1:11" ht="30" customHeight="1"/>
+    <row r="58" spans="1:11" ht="30" customHeight="1"/>
+    <row r="59" spans="1:11" ht="30" customHeight="1"/>
+    <row r="60" spans="1:11" ht="30" customHeight="1"/>
+    <row r="61" spans="1:11" ht="30" customHeight="1"/>
+    <row r="62" spans="1:11" ht="30" customHeight="1"/>
+    <row r="63" spans="1:11" ht="30" customHeight="1"/>
+    <row r="64" spans="1:11" ht="30" customHeight="1"/>
     <row r="65" ht="30" customHeight="1"/>
     <row r="66" ht="30" customHeight="1"/>
     <row r="67" ht="30" customHeight="1"/>
@@ -3191,10 +2737,7 @@
     <row r="87" ht="30" customHeight="1"/>
     <row r="88" ht="30" customHeight="1"/>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:I48" etc:filterBottomFollowUsedRange="0">
-    <extLst/>
-  </autoFilter>
+  <autoFilter ref="A1:I53" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>